--- a/samples/reports/receipt/template.xlsx
+++ b/samples/reports/receipt/template.xlsx
@@ -5,7 +5,7 @@
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'領収書'!$A$1:$D$13,'領収書'!$A$16:$D$28</x:definedName>
   </x:definedNames>
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="領収書" sheetId="1" r:id="Rc47b81dd77464ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="領収書" sheetId="1" r:id="R6698aeb2df3d496b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -205,6 +205,8 @@
       <x:c r="B5" s="9">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="C5" s="9"/>
+      <x:c r="D5" s="9"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="12" t="inlineStr">
@@ -217,6 +219,8 @@
           <x:t>サンプル代金として</x:t>
         </x:is>
       </x:c>
+      <x:c r="C7" s="5"/>
+      <x:c r="D7" s="5"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="3" t="inlineStr">
@@ -271,6 +275,8 @@
       <x:c r="B20" s="9">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="C20" s="9"/>
+      <x:c r="D20" s="9"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="12" t="inlineStr">
@@ -283,6 +289,8 @@
           <x:t>サンプル代金として</x:t>
         </x:is>
       </x:c>
+      <x:c r="C22" s="5"/>
+      <x:c r="D22" s="5"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="3" t="inlineStr">
